--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,8 @@
           <t>2026-09-20 07:06:56</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -533,6 +531,292 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:45:45</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:45:45</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:17:12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana )</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:17:12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella )</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:17:12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo )</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,10 +652,8 @@
           <t>2026-09-20 08:17:12</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -710,10 +708,8 @@
           <t>2026-09-20 08:17:12</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B6" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -768,10 +764,8 @@
           <t>2026-09-20 08:17:12</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B7" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -817,6 +811,1300 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo )</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:53:29</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 08/08/2026  Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:53:29</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mulai Tanggal 08/08/2026 Operator Crane Shift Siang atas nama Wanhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:53:29</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 08/08/2026 Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:53:29</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Siang  atas nama Tison</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:53:29</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:53:29</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:53:29</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:04:59</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:09</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:09</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:09</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:09</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:16:09</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:27:42</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:27:42</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:27:42</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:27:42</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Mulai tanggal 08/08/2026 Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:27:42</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:27:42</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Mulai tanggal 08/08/2026 Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:35:51</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 08/08/2026 Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:35:51</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 23/08/2026  Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:35:51</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 09/08/2026 Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,13 +1937,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 11:35:51</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-21 09:03:56</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1995,13 +1993,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20 11:35:51</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-21 09:03:56</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2053,13 +2049,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-20 11:35:51</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-21 09:03:56</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2105,6 +2099,176 @@
       <c r="L30" t="inlineStr">
         <is>
           <t>Mulai Tanggal 09/08/2026 Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-21 09:40:47</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:25:42</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:09:22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -1265,7 +1265,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:09</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1291,37 +1291,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:09</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1347,37 +1347,37 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:09</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1403,37 +1403,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:09</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1459,37 +1459,37 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Mulai tanggal 08/08/2026 Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:09</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1515,37 +1515,37 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 10:16:09</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1571,37 +1571,37 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Mulai tanggal 08/08/2026 Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 09:03:56</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1645,19 +1645,19 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 08/08/2026 Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 09:03:56</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1701,19 +1701,19 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 23/08/2026  Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 09:03:56</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1757,19 +1757,19 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 09/08/2026 Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 09:40:47</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1787,20 +1787,20 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1808,24 +1808,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Mulai tanggal 08/08/2026 Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 11:25:42</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1843,45 +1843,45 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 12:09:22</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1899,53 +1899,55 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Mulai tanggal 08/08/2026 Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1955,7 +1957,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1963,45 +1965,47 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2011,7 +2015,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2019,45 +2023,47 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 23/08/2026  Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2067,7 +2073,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2080,15 +2086,15 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2098,22 +2104,24 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 09/08/2026 Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21 09:40:47</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2123,11 +2131,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2136,40 +2144,42 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-21 11:25:42</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:56:14</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2179,20 +2189,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2200,24 +2210,24 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21 12:09:22</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2227,7 +2237,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2237,20 +2247,20 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2258,7 +2268,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2268,7 +2278,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,7 +1769,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21 09:40:47</t>
+          <t>2026-09-21 11:25:42</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1795,20 +1795,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1818,14 +1818,14 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21 11:25:42</t>
+          <t>2026-09-21 12:09:22</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21 12:09:22</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
@@ -1940,10 +1940,8 @@
           <t>2026-09-22 10:56:14</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B28" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1961,7 +1959,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1970,7 +1968,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1988,7 +1986,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
@@ -1998,10 +1996,8 @@
           <t>2026-09-22 10:56:14</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B29" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2019,16 +2015,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2046,7 +2042,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
@@ -2056,10 +2052,8 @@
           <t>2026-09-22 10:56:14</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B30" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2077,7 +2071,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2104,7 +2098,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
@@ -2114,10 +2108,8 @@
           <t>2026-09-22 10:56:14</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B31" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2135,7 +2127,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2144,7 +2136,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2162,7 +2154,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
@@ -2172,10 +2164,8 @@
           <t>2026-09-22 10:56:14</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B32" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2193,7 +2183,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2227,17 +2217,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-24 08:24:36</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2247,20 +2235,20 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2268,17 +2256,75 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t xml:space="preserve">Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:50:46</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -817,7 +817,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 09:53:29</t>
+          <t>2026-09-20 10:04:59</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -856,24 +856,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026  Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 09:53:29</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -891,20 +891,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -912,24 +912,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mulai Tanggal 08/08/2026 Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 09:53:29</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -947,20 +947,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -968,24 +968,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 09:53:29</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1003,20 +1003,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1024,24 +1024,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 09:53:29</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1080,24 +1080,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Mulai tanggal 08/08/2026 Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 09:53:29</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1115,20 +1115,20 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1136,24 +1136,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 09:53:29</t>
+          <t>2026-09-20 10:27:42</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1171,20 +1171,20 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1192,24 +1192,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Mulai tanggal 08/08/2026 Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 10:04:59</t>
+          <t>2026-09-21 09:03:56</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>024A/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1253,19 +1253,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Mulai Tanggal 08/08/2026 Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 09:03:56</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1283,20 +1283,20 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1309,19 +1309,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 23/08/2026  Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 09:03:56</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1339,20 +1339,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1365,19 +1365,19 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 09/08/2026 Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 11:25:42</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1395,45 +1395,45 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-21 12:09:22</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1451,45 +1451,45 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Mulai tanggal 08/08/2026 Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1507,45 +1507,45 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1563,45 +1563,45 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Mulai tanggal 08/08/2026 Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1619,11 +1619,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1632,32 +1632,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 23/08/2026  Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1731,11 +1731,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1744,15 +1744,15 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1762,14 +1762,14 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 09/08/2026 Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21 11:25:42</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1787,20 +1787,20 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1808,24 +1808,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21 12:09:22</t>
+          <t>2026-09-24 08:24:36</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t xml:space="preserve">Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
+          <t>2026-09-24 09:50:46</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1907,45 +1907,47 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:01:55</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1955,53 +1957,55 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Mulai Tanggal 08/08/2026  Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:01:55</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2011,53 +2015,55 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t xml:space="preserve"> Mulai Tanggal 23/08/2026 Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:01:55</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2067,53 +2073,55 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Mulai Tanggal 08/08/2026 Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:01:55</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2123,53 +2131,55 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:01:55</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2179,53 +2189,55 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-24 08:24:36</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>7201250141</v>
+          <t>2026-09-30 11:01:55</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2235,45 +2247,45 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro </t>
+          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:46</t>
+          <t>2026-09-30 11:01:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2283,7 +2295,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2297,16 +2309,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2314,17 +2326,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -649,7 +649,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 08:17:12</t>
+          <t>2026-09-20 10:04:59</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -693,19 +693,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana )</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 08:17:12</t>
+          <t>2026-09-21 12:09:22</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -723,45 +723,45 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella )</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 08:17:12</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -779,45 +779,45 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo )</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 10:04:59</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>024A/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -835,45 +835,45 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PERSONEL ON CALL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -891,45 +891,45 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -947,45 +947,45 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1003,45 +1003,45 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-22 10:56:14</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1059,45 +1059,45 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Mulai tanggal 08/08/2026 Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-24 08:24:36</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1115,11 +1115,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,11 +1128,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1141,19 +1141,19 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t xml:space="preserve">Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 10:27:42</t>
+          <t>2026-09-24 09:50:46</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1171,20 +1171,20 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1202,14 +1202,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Mulai tanggal 08/08/2026 Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
+          <t>2026-09-30 11:48:13</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1258,14 +1258,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 08/08/2026  Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
+          <t>2026-09-30 11:48:13</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1314,14 +1314,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 23/08/2026  Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t xml:space="preserve"> Mulai Tanggal 23/08/2026 Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21 09:03:56</t>
+          <t>2026-09-30 11:48:13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1360,24 +1360,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 09/08/2026 Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mulai Tanggal 08/08/2026 Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21 11:25:42</t>
+          <t>2026-09-30 11:48:13</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1408,11 +1408,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1426,14 +1426,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
+          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21 12:09:22</t>
+          <t>2026-09-30 11:48:13</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1451,45 +1451,45 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
+          <t>2026-09-30 11:48:13</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1507,28 +1507,28 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1538,14 +1538,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
+          <t>2026-09-30 11:48:13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1563,28 +1563,28 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
+          <t>2026-09-30 11:58:30</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1619,45 +1619,45 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana )</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
+          <t>2026-09-30 11:58:30</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1675,45 +1675,45 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella )</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
+          <t>2026-09-30 11:58:30</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1731,45 +1731,45 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo )</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-22 10:56:14</t>
+          <t>2026-09-30 12:10:06</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1787,45 +1787,45 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Mulai Pekerjaan 07/08/2026  Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-24 08:24:36</t>
+          <t>2026-09-30 12:10:06</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1843,11 +1843,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1869,19 +1869,19 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro </t>
+          <t>Mulai Pekerjaan  07/08/2026 Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:46</t>
+          <t>2026-09-30 12:10:06</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1899,20 +1899,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1920,34 +1920,32 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Mulai Pekerjaan 07/08/2026  Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-30 11:01:55</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:10:06</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1957,20 +1955,20 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1978,34 +1976,32 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026  Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Mulai tanggal 11/08/2026 Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-30 11:01:55</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:10:06</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2015,20 +2011,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2036,34 +2032,32 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mulai Tanggal 23/08/2026 Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Mulai tanggal  07/08/2026 Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-30 11:01:55</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:10:06</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2073,20 +2067,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2094,7 +2088,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2104,24 +2098,22 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Mulai tanggal 08/08/2026 Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-30 11:01:55</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:16:43</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2135,16 +2127,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2152,7 +2144,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2162,24 +2154,22 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Mulai Tanggal 08/08/2026 Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-30 11:01:55</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:16:43</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2193,16 +2183,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2210,34 +2200,32 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 08/08/2026 Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Mulai Tanggal 23/08/2026  Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-30 11:01:55</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:16:43</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2251,16 +2239,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2268,7 +2256,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2278,14 +2266,14 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Mulai Tanggal 09/08/2026 Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-30 11:01:55</t>
+          <t>2026-09-30 12:24:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2295,7 +2283,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2309,7 +2297,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2318,11 +2306,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2331,12 +2319,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Mulai Tanggal 09/08/2026 Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2276,10 +2276,8 @@
           <t>2026-09-30 12:24:51</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B34" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2325,6 +2323,64 @@
       <c r="L34" t="inlineStr">
         <is>
           <t>Mulai Tanggal 08/08/2026 Upah harian Flagman  di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:44:29</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/X/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear  Mulai tanggal 07 Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2332,55 +2332,167 @@
           <t>2026-10-01 13:44:29</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/X/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear  Mulai tanggal 07 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:16:37</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>036/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Mulai tanggal 07 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:41:20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>At Cost + Fee 15%</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear  Mulai tanggal 07 Agustus 2026</t>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Mulai tanggal 07 Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,55 +2444,623 @@
           <t>2026-10-02 09:41:20</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Mulai tanggal 07 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:07</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:07</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:07</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:07</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:56:07</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:37</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>PROVISIONAL SUM</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>At Cost + Fee 15%</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Mulai tanggal 07 Agustus 2026</t>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:37</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:37</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:37</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>4</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:37</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2780,10 +2780,8 @@
           <t>2026-10-03 13:04:37</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B43" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2838,10 +2836,8 @@
           <t>2026-10-03 13:04:37</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B44" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2896,10 +2892,8 @@
           <t>2026-10-03 13:04:37</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B45" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2954,10 +2948,8 @@
           <t>2026-10-03 13:04:37</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B46" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3012,10 +3004,8 @@
           <t>2026-10-03 13:04:37</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B47" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3061,6 +3051,1192 @@
       <c r="L47" t="inlineStr">
         <is>
           <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:51:05</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, main course</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:51:05</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:13:17</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>040/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:36:32</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:36:32</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella) Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:36:32</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo) Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:20:59</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Siang atas Nama Wanhar Renaldi Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:20:59</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Malam atas Nama Ilsan Adjedar Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:20:59</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>RIgger Crane Shift Siang atas Nama Tison Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:20:59</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>4</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:20:59</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:20:59</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:41:57</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto Mulai tanggal 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:26:59</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Mulai tgl 4 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:57:19</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:57:19</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi Mulai 01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:27:37</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:27:37</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:27:37</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:27:37</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:27:37</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3953,13 +3953,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-06 13:27:37</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-06 16:48:51</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -4011,13 +4009,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-06 13:27:37</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-06 16:48:51</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -4069,13 +4065,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-06 13:27:37</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-06 16:48:51</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -4127,13 +4121,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-06 13:27:37</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-06 16:48:51</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -4185,13 +4177,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-06 13:27:37</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-06 16:48:51</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -4237,6 +4227,456 @@
       <c r="L68" t="inlineStr">
         <is>
           <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:21:38</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT, Support Well Services Senoro Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:21:38</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)  Support Well Services Senoro Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:21:38</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:21:38</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:21:38</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>5</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories, Operasi Shift Malam Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:21:38</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Shift Malam Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:55:09</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>048/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:05:27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>050/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -4233,7 +4233,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-06 17:21:38</t>
+          <t>2026-10-06 17:55:09</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4282,14 +4282,14 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT, Support Well Services Senoro Mulai 01  September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-06 17:21:38</t>
+          <t>2026-10-06 19:05:27</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4311,24 +4311,24 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4338,18 +4338,20 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)  Support Well Services Senoro Mulai 01  September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-06 17:21:38</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:14:37</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4367,16 +4369,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4394,18 +4396,20 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang Mulai 01  September 2026</t>
+          <t>Support Well Services Senoro Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-06 17:21:38</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:14:37</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4423,16 +4427,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4450,18 +4454,20 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam Mulai 01  September 2026</t>
+          <t xml:space="preserve"> Support Well Services Senoro Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-06 17:21:38</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:14:37</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4479,7 +4485,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4488,7 +4494,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4506,18 +4512,20 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories, Operasi Shift Malam Mulai 01  September 2026</t>
+          <t>Operasi Shift Siang Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-06 17:21:38</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:14:37</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4535,7 +4543,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4544,7 +4552,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4562,22 +4570,24 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Shift Malam Mulai 01  September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-06 17:55:09</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>7201250141</v>
+          <t>2026-10-07 06:14:37</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4591,16 +4601,16 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4608,7 +4618,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4618,14 +4628,14 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-06 19:05:27</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4635,7 +4645,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4649,24 +4659,24 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4676,7 +4686,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4348,10 +4348,8 @@
           <t>2026-10-07 06:14:37</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B71" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4406,10 +4404,8 @@
           <t>2026-10-07 06:14:37</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B72" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4464,10 +4460,8 @@
           <t>2026-10-07 06:14:37</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B73" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4522,10 +4516,8 @@
           <t>2026-10-07 06:14:37</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B74" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4580,10 +4572,8 @@
           <t>2026-10-07 06:14:37</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B75" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4638,10 +4628,8 @@
           <t>2026-10-07 06:14:37</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B76" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4687,6 +4675,800 @@
       <c r="L76" t="inlineStr">
         <is>
           <t>Operasi Shift Malam Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:42:47</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:42:47</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:01:02</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:01:02</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:16</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:16</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:16</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:16</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:33:16</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:35:04</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:35:04</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:35:04</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:35:04</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:35:04</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>5</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3057,7 +3057,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-06 09:51:05</t>
+          <t>2026-10-06 10:13:17</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3083,20 +3083,20 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-06 09:51:05</t>
+          <t>2026-10-06 10:36:32</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3135,24 +3135,24 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3162,14 +3162,14 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-06 10:13:17</t>
+          <t>2026-10-06 10:36:32</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Mulai tanggal 01 September 2026</t>
+          <t>Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella) Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) Mulai tanggal 01 September 2026</t>
+          <t>Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo) Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-06 10:36:32</t>
+          <t>2026-10-06 11:20:59</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3330,14 +3330,14 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella) Mulai tanggal 01 September 2026</t>
+          <t>Operator Crane Shift Siang atas Nama Wanhar Renaldi Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-06 10:36:32</t>
+          <t>2026-10-06 11:20:59</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo) Mulai tanggal 01 September 2026</t>
+          <t>Operator Crane Shift Malam atas Nama Ilsan Adjedar Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas Nama Wanhar Renaldi Mulai tanggal 01 September 2026</t>
+          <t>RIgger Crane Shift Siang atas Nama Tison Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam atas Nama Ilsan Adjedar Mulai tanggal 01 September 2026</t>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>RIgger Crane Shift Siang atas Nama Tison Mulai tanggal 01 September 2026</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3610,14 +3610,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata Mulai tanggal 01 September 2026</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-06 11:20:59</t>
+          <t>2026-10-06 11:41:57</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng Mulai tanggal 01 September 2026</t>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto Mulai tanggal 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-06 11:20:59</t>
+          <t>2026-10-06 12:26:59</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3704,32 +3704,32 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani Mulai tanggal 01 September 2026</t>
+          <t>PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Mulai tgl 4 September 2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-06 11:41:57</t>
+          <t>2026-10-06 12:57:19</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3778,14 +3778,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto Mulai tanggal 01 September 2026</t>
+          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-06 12:26:59</t>
+          <t>2026-10-06 12:57:19</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3803,45 +3803,45 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Mulai tgl 4 September 2026</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi Mulai 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-06 12:57:19</t>
+          <t>2026-10-06 16:48:51</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi Mulai 01  September 2026</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-06 12:57:19</t>
+          <t>2026-10-06 16:48:51</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi Mulai 01 September 2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4109,19 +4109,19 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-06 16:48:51</t>
+          <t>2026-10-06 17:55:09</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4143,24 +4143,24 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4170,14 +4170,14 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-06 16:48:51</t>
+          <t>2026-10-06 19:05:27</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4199,16 +4199,16 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4226,14 +4226,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-06 17:55:09</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4282,14 +4282,14 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
+          <t>Support Well Services Senoro Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-06 19:05:27</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4311,24 +4311,24 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
+          <t xml:space="preserve"> Support Well Services Senoro Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4367,16 +4367,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Mulai 01  September 2026</t>
+          <t>Operasi Shift Siang Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4423,16 +4423,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Support Well Services Senoro Mulai 01  September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Mulai 01  September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4569,7 +4569,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-07 06:14:37</t>
+          <t>2026-10-07 08:42:47</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4587,11 +4587,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4600,32 +4600,32 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Mulai 01  September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-07 06:14:37</t>
+          <t>2026-10-07 08:42:47</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4643,11 +4643,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4656,32 +4656,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Mulai 01  September 2026</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:47</t>
+          <t>2026-10-07 09:01:02</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:47</t>
+          <t>2026-10-07 09:01:02</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4786,14 +4786,14 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:02</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -4819,12 +4819,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4837,19 +4837,19 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:02</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5066,14 +5066,14 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5091,11 +5091,11 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -5117,19 +5117,19 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5147,11 +5147,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -5168,17 +5168,17 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -5188,10 +5188,8 @@
           <t>2026-10-07 10:35:04</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B86" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -5209,7 +5207,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5218,7 +5216,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5236,7 +5234,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
@@ -5246,10 +5244,8 @@
           <t>2026-10-07 10:35:04</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B87" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -5267,16 +5263,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -5294,7 +5290,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
@@ -5304,10 +5300,8 @@
           <t>2026-10-07 10:35:04</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B88" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -5325,16 +5319,16 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -5342,7 +5336,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5352,24 +5346,22 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-07 11:29:01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5379,11 +5371,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5405,70 +5397,240 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
+          <t>2026-10-07 11:29:01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:29:01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2 Mulai tgl 29 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:58:01</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>5</v>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, main course</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:58:01</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -3841,7 +3841,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-06 16:48:51</t>
+          <t>2026-10-06 17:55:09</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3867,20 +3867,20 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-06 16:48:51</t>
+          <t>2026-10-06 19:05:27</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3919,16 +3919,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3946,14 +3946,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-06 16:48:51</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3975,41 +3975,41 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
+          <t>Support Well Services Senoro Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-06 16:48:51</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4031,24 +4031,24 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4058,14 +4058,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t xml:space="preserve"> Support Well Services Senoro Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-06 16:48:51</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4087,24 +4087,24 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4114,14 +4114,14 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Operasi Shift Siang Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-06 17:55:09</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4143,16 +4143,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4170,14 +4170,14 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-06 19:05:27</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4199,24 +4199,24 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4255,16 +4255,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4282,14 +4282,14 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Mulai 01  September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-07 06:14:37</t>
+          <t>2026-10-07 08:42:47</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4307,45 +4307,45 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Support Well Services Senoro Mulai 01  September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-07 06:14:37</t>
+          <t>2026-10-07 08:42:47</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4363,11 +4363,11 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4376,32 +4376,32 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Mulai 01  September 2026</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-07 06:14:37</t>
+          <t>2026-10-07 09:01:02</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4419,45 +4419,45 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Mulai 01  September 2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-07 06:14:37</t>
+          <t>2026-10-07 09:01:02</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4475,45 +4475,45 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Mulai 01  September 2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-07 06:14:37</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4531,45 +4531,45 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Mulai 01  September 2026</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:47</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4587,20 +4587,20 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4613,19 +4613,19 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:47</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4643,20 +4643,20 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4669,19 +4669,19 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:02</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4699,20 +4699,20 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4725,19 +4725,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:02</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4755,20 +4755,20 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4837,19 +4837,19 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4905,7 +4905,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4949,19 +4949,19 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5005,19 +5005,19 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -5061,19 +5061,19 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
+          <t>2026-10-07 11:29:01</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -5117,19 +5117,19 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
+          <t>2026-10-07 11:29:01</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -5173,19 +5173,19 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
+          <t>2026-10-07 11:29:01</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5229,19 +5229,19 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2 Mulai tgl 29 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
+          <t>2026-10-07 11:58:01</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5259,11 +5259,11 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5272,32 +5272,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
+          <t>2026-10-07 11:58:01</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5315,11 +5315,11 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5328,11 +5328,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5341,27 +5341,29 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-07 11:29:01</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:58:33</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5371,7 +5373,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5379,12 +5381,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -5392,32 +5394,34 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-07 11:29:01</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:58:33</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5427,7 +5431,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -5435,12 +5439,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5448,32 +5452,34 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-07 11:29:01</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:58:33</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5483,7 +5489,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5491,12 +5497,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5504,24 +5510,24 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2 Mulai tgl 29 Agustus 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:01</t>
+          <t>2026-10-10 08:58:33</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5531,7 +5537,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5545,24 +5551,24 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5572,14 +5578,14 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:01</t>
+          <t>2026-10-10 08:58:33</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5589,7 +5595,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5603,24 +5609,24 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5630,7 +5636,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -3841,7 +3841,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-06 17:55:09</t>
+          <t>2026-10-06 19:05:27</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3867,20 +3867,20 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-06 19:05:27</t>
+          <t>2026-10-07 06:14:37</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3923,20 +3923,20 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili  Mulai 01 September 2026</t>
+          <t>Support Well Services Senoro Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Mulai 01  September 2026</t>
+          <t xml:space="preserve"> Support Well Services Senoro Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4031,16 +4031,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Support Well Services Senoro Mulai 01  September 2026</t>
+          <t>Operasi Shift Siang Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Mulai 01  September 2026</t>
+          <t>Operasi Shift Malam Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-07 06:14:37</t>
+          <t>2026-10-07 08:42:47</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4264,25 +4264,25 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Mulai 01  September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4338,14 +4338,14 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:47</t>
+          <t>2026-10-07 09:01:02</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4367,16 +4367,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4450,14 +4450,14 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:02</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4475,20 +4475,20 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4755,11 +4755,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4776,17 +4776,17 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
@@ -4927,16 +4927,16 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5010,14 +5010,14 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
+          <t>2026-10-07 11:29:01</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5035,11 +5035,11 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5056,17 +5056,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -5151,16 +5151,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -5173,19 +5173,19 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2 Mulai tgl 29 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-07 11:29:01</t>
+          <t>2026-10-07 11:58:01</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5203,38 +5203,38 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2 Mulai tgl 29 Agustus 2026</t>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -5290,14 +5290,14 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:01</t>
+          <t>2026-10-10 08:58:33</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5319,24 +5319,24 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -5356,10 +5356,8 @@
           <t>2026-10-10 08:58:33</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B89" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -5377,7 +5375,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5404,7 +5402,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -5414,10 +5412,8 @@
           <t>2026-10-10 08:58:33</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B90" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -5435,7 +5431,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5457,12 +5453,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
         </is>
       </c>
     </row>
@@ -5472,10 +5468,8 @@
           <t>2026-10-10 08:58:33</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B91" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -5493,7 +5487,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5502,7 +5496,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5515,12 +5509,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -5530,10 +5524,8 @@
           <t>2026-10-10 08:58:33</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B92" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -5551,7 +5543,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5578,14 +5570,14 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-10 08:58:33</t>
+          <t>2026-10-10 12:30:03</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5595,7 +5587,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5609,24 +5601,24 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5636,7 +5628,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5580,10 +5580,8 @@
           <t>2026-10-10 12:30:03</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B93" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5629,6 +5627,120 @@
       <c r="L93" t="inlineStr">
         <is>
           <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:27:28</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:35:59</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>052/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5185,7 +5185,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:01</t>
+          <t>2026-10-10 08:58:33</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5211,20 +5211,20 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-07 11:58:01</t>
+          <t>2026-10-10 08:58:33</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5267,20 +5267,20 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5341,12 +5341,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5453,19 +5453,19 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-10 08:58:33</t>
+          <t>2026-10-10 12:30:03</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5487,24 +5487,24 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5514,14 +5514,14 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-10 08:58:33</t>
+          <t>2026-10-13 10:27:28</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5539,20 +5539,20 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5560,24 +5560,24 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-10 12:30:03</t>
+          <t>2026-10-13 10:35:59</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5603,37 +5603,37 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-13 10:27:28</t>
+          <t>2026-10-15 17:38:47</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -5659,16 +5659,16 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5677,70 +5677,184 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational Consumption</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-13 10:35:59</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
+          <t>2026-10-15 17:38:47</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Operational side consumption</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1157</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:45:05</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>PROVISIONAL SUM</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>At Cost + Fee 15%</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>operational consumption</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:45:05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Operational side consumption</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bamp_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4233,7 +4233,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:47</t>
+          <t>2026-10-07 09:01:02</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4282,14 +4282,14 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:47</t>
+          <t>2026-10-07 09:01:02</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4338,14 +4338,14 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:02</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4389,19 +4389,19 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-07 09:01:02</t>
+          <t>2026-10-07 09:33:16</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4618,14 +4618,14 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4643,11 +4643,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4669,19 +4669,19 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-07 09:33:16</t>
+          <t>2026-10-07 10:35:04</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4699,11 +4699,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4720,17 +4720,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
@@ -4871,16 +4871,16 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4898,14 +4898,14 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
+          <t>2026-10-07 11:29:01</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4923,11 +4923,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4949,19 +4949,19 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-07 10:35:04</t>
+          <t>2026-10-07 11:29:01</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5000,17 +5000,17 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA Demobilisasi portacamp Office 40 feet dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -5039,16 +5039,16 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -5061,19 +5061,19 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2 Mulai tgl 29 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-07 11:29:01</t>
+          <t>2026-10-10 08:58:33</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5091,20 +5091,20 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -5112,24 +5112,24 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro Mulai tgl 23 Agustus 2026</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-07 11:29:01</t>
+          <t>2026-10-10 08:58:33</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5147,20 +5147,20 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -5168,17 +5168,17 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2 Mulai tgl 29 Agustus 2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -5341,19 +5341,19 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Mulai  tanggal 27  September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-10 08:58:33</t>
+          <t>2026-10-10 12:30:03</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5375,24 +5375,24 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5402,14 +5402,14 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-10 08:58:33</t>
+          <t>2026-10-13 10:27:28</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5427,20 +5427,20 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5448,24 +5448,24 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Mulai  tanggal 01  September 2026</t>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-10 12:30:03</t>
+          <t>2026-10-13 10:35:59</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5491,37 +5491,37 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Mulai 01  September 2026</t>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-13 10:27:28</t>
+          <t>2026-10-15 17:45:05</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -5547,16 +5547,16 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5565,19 +5565,19 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-13 10:35:59</t>
+          <t>2026-10-15 17:45:05</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5595,24 +5595,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Operational side consumption</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5621,19 +5621,19 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-15 17:38:47</t>
+          <t>2026-10-16 10:23:41</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2578</v>
+        <v>0</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-15 17:38:47</t>
+          <t>2026-10-16 10:23:41</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1157</v>
+        <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-15 17:45:05</t>
+          <t>2026-10-16 11:51:11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -5773,16 +5773,16 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>operational consumption</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5791,70 +5791,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>DDITIONAL CAMP SERVICES, Operational Consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-10-15 17:45:05</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>2</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Operational side consumption</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Mobilisasi 2 Unit Lighting Tower dan 2 Unit Mesin Genset 80 KVA dari Luwuk ke Senoro Cluster B</t>
         </is>
       </c>
     </row>
